--- a/customer_profiles/ro/templates/emax/invoice&pl.xlsx
+++ b/customer_profiles/ro/templates/emax/invoice&pl.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JOYCE\Desktop\赛肯单据生成工具\赛肯单据生成工具\_internal\templates\emax\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="23840" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="CI" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="47">
   <si>
     <t>E MAX SPORT PTE. LTD.</t>
   </si>
@@ -114,7 +119,10 @@
     <t>ORIGIN IN CHINA</t>
   </si>
   <si>
-    <t>PACKED IN 30 CTNS</t>
+    <t xml:space="preserve">PACKED IN </t>
+  </si>
+  <si>
+    <t>CTNS</t>
   </si>
   <si>
     <t>THERE IS NO SOLID WOOD PACKING MATERIAL IN THIS SHIPMENT.</t>
@@ -156,9 +164,6 @@
     <t>Measurement</t>
   </si>
   <si>
-    <t>CTNS</t>
-  </si>
-  <si>
     <t>TOTAL:</t>
   </si>
   <si>
@@ -169,9 +174,6 @@
   </si>
   <si>
     <t>CBM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACKED IN </t>
   </si>
   <si>
     <t xml:space="preserve"> CTNS</t>
@@ -191,14 +193,14 @@
     <numFmt numFmtId="176" formatCode="[$$-409]#,##0.00;\-[$$-409]#,##0.00"/>
     <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="178" formatCode="[$-409]d/mmm/yy;@"/>
-    <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="180" formatCode="0.0"/>
-    <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="180" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="181" formatCode="0.0"/>
     <numFmt numFmtId="182" formatCode="0.00_ "/>
     <numFmt numFmtId="183" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="184" formatCode="\$#,##0.00;\-\$#,##0.00"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="39">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -210,10 +212,15 @@
       <charset val="0"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="20"/>
       <color theme="3" tint="0.399975585192419"/>
-      <name val="宋体"/>
+      <name val="Bauhaus 93"/>
       <charset val="134"/>
     </font>
     <font>
@@ -225,44 +232,7 @@
     <font>
       <b/>
       <sz val="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="3" tint="0.399975585192419"/>
-      <name val="Bauhaus 93"/>
+      <name val="Arial Black"/>
       <charset val="134"/>
     </font>
     <font>
@@ -273,12 +243,30 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <name val="Arial Black"/>
-      <charset val="134"/>
+      <u/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="0"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -297,16 +285,9 @@
     </font>
     <font>
       <b/>
-      <u/>
       <sz val="12"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -825,176 +806,180 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="33" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="176" fontId="36" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="37" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="37" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="39" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="40" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="40" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1006,256 +991,234 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="61" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="61" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="55" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="26" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="178" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="62" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="25" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="26" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="25" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="55" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="26" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="184" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="63">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1678,464 +1641,480 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="3.83035714285714" style="50" customWidth="1"/>
-    <col min="2" max="2" width="12.3303571428571" style="50" customWidth="1"/>
-    <col min="3" max="3" width="33.75" style="50" customWidth="1"/>
-    <col min="4" max="4" width="19.3303571428571" style="51" customWidth="1"/>
-    <col min="5" max="5" width="10.25" style="52" customWidth="1"/>
-    <col min="6" max="6" width="9" style="53" customWidth="1"/>
-    <col min="7" max="7" width="8.875" style="50" customWidth="1"/>
-    <col min="8" max="8" width="17.375" style="54" customWidth="1"/>
-    <col min="9" max="9" width="12.25" style="54" customWidth="1"/>
-    <col min="10" max="10" width="9" style="55" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="50" customWidth="1"/>
+    <col min="1" max="1" width="13.025" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.3333333333333" style="4" customWidth="1"/>
+    <col min="3" max="3" width="33.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="19.3333333333333" style="11" customWidth="1"/>
+    <col min="5" max="5" width="10.25" style="12" customWidth="1"/>
+    <col min="6" max="6" width="9" style="13" customWidth="1"/>
+    <col min="7" max="7" width="8.875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="14" customWidth="1"/>
+    <col min="9" max="9" width="12.25" style="14" customWidth="1"/>
+    <col min="10" max="10" width="9" style="61" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.8" customHeight="1" spans="1:10">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="57"/>
+      <c r="I1" s="62"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="57"/>
+      <c r="I2" s="62"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="57"/>
+      <c r="I3" s="62"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="62" t="s">
+      <c r="G5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="H5" s="52"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="50"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="64" t="s">
+      <c r="H6" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="65"/>
-      <c r="J6" s="50"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="52" t="s">
+      <c r="H7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="66"/>
-      <c r="J7" s="50"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="60"/>
-      <c r="B8" s="60"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
       <c r="H8" s="67"/>
-      <c r="I8" s="66"/>
-      <c r="J8" s="50"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="69"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
+      <c r="B9" s="24"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
       <c r="H9" s="67"/>
-      <c r="I9" s="66"/>
-      <c r="J9" s="50"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="69" t="s">
+      <c r="A10" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="24" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="66"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="50"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="42"/>
-      <c r="B12" s="70" t="s">
+      <c r="A12" s="68"/>
+      <c r="B12" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="70" t="s">
+      <c r="D12" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="71" t="s">
+      <c r="E12" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="71" t="s">
+      <c r="H12" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="55"/>
-      <c r="J12" s="50"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="73"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73" t="s">
+      <c r="A13" s="72"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="74" t="s">
+      <c r="D13" s="72"/>
+      <c r="E13" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="75"/>
-      <c r="G13" s="76"/>
-      <c r="H13" s="74" t="s">
+      <c r="F13" s="74"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="55"/>
-      <c r="J13" s="50"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="B14" s="77"/>
-      <c r="C14" s="78" t="s">
+      <c r="B14" s="76"/>
+      <c r="C14" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="79"/>
-      <c r="E14" s="80"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="50"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="61"/>
+      <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="79"/>
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="50"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="61"/>
+      <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="79"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="84"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="50"/>
+      <c r="A16" s="41"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
+      <c r="D16" s="76"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="79"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="84"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="50"/>
+      <c r="A17" s="41"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="76"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="4"/>
     </row>
     <row r="18" spans="1:10">
-      <c r="A18" s="79"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="77"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="50"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="76"/>
+      <c r="C18" s="76"/>
+      <c r="D18" s="76"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="76"/>
+      <c r="H18" s="76"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="86">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="84">
         <v>304</v>
       </c>
-      <c r="G19" s="51"/>
-      <c r="H19" s="87">
+      <c r="G19" s="11"/>
+      <c r="H19" s="85">
         <v>2506.64</v>
       </c>
-      <c r="I19" s="55"/>
-      <c r="J19" s="50"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="4"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="88"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="85"/>
-      <c r="F20" s="42"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="50"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="83"/>
+      <c r="F20" s="68"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="4"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="A21" s="90" t="s">
+      <c r="A21" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="85"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="83"/>
       <c r="I21" s="67"/>
-      <c r="J21" s="50"/>
+      <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="90" t="s">
+      <c r="A22" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="90"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="85"/>
+      <c r="B22" s="76">
+        <f>PL!B20</f>
+        <v>0</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="83"/>
       <c r="I22" s="67"/>
-      <c r="J22" s="50"/>
+      <c r="J22" s="4"/>
     </row>
     <row r="23" spans="1:10">
-      <c r="A23" s="90" t="s">
-        <v>28</v>
+      <c r="A23" s="53" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="G27" s="91"/>
+      <c r="G27" s="87"/>
     </row>
     <row r="31" spans="1:10">
-      <c r="A31" s="52"/>
-      <c r="B31" s="52"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="92"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="93"/>
-      <c r="F33" s="94"/>
-      <c r="G33" s="95"/>
-      <c r="H33" s="96"/>
-      <c r="I33" s="96"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="91"/>
+      <c r="I33" s="91"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="H34" s="97"/>
-      <c r="I34" s="97"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="H34" s="92"/>
+      <c r="I34" s="92"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="E35" s="93"/>
-      <c r="F35" s="94"/>
-      <c r="G35" s="98"/>
-      <c r="H35" s="96"/>
-      <c r="I35" s="96"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="E35" s="88"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="91"/>
+      <c r="I35" s="91"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="H36" s="97"/>
-      <c r="I36" s="97"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="H36" s="92"/>
+      <c r="I36" s="92"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="H37" s="97"/>
-      <c r="I37" s="97"/>
+      <c r="A37" s="12"/>
+      <c r="B37" s="12"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="H38" s="97"/>
-      <c r="I38" s="97"/>
+      <c r="H38" s="92"/>
+      <c r="I38" s="92"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="H39" s="97"/>
-      <c r="I39" s="97"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="92"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="H40" s="97"/>
-      <c r="I40" s="97"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="92"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="H41" s="97"/>
-      <c r="I41" s="97"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="H42" s="97"/>
-      <c r="I42" s="97"/>
+      <c r="H42" s="92"/>
+      <c r="I42" s="92"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="H43" s="97"/>
-      <c r="I43" s="97"/>
+      <c r="H43" s="92"/>
+      <c r="I43" s="92"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="H44" s="97"/>
-      <c r="I44" s="97"/>
+      <c r="H44" s="92"/>
+      <c r="I44" s="92"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="H45" s="97"/>
-      <c r="I45" s="97"/>
+      <c r="H45" s="92"/>
+      <c r="I45" s="92"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="H46" s="97"/>
-      <c r="I46" s="97"/>
+      <c r="H46" s="92"/>
+      <c r="I46" s="92"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="H47" s="97"/>
-      <c r="I47" s="97"/>
+      <c r="H47" s="92"/>
+      <c r="I47" s="92"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="H48" s="97"/>
-      <c r="I48" s="97"/>
+      <c r="H48" s="92"/>
+      <c r="I48" s="92"/>
     </row>
     <row r="49" spans="7:9">
-      <c r="H49" s="97"/>
-      <c r="I49" s="97"/>
+      <c r="H49" s="92"/>
+      <c r="I49" s="92"/>
     </row>
     <row r="50" spans="7:9">
-      <c r="H50" s="97"/>
-      <c r="I50" s="97"/>
+      <c r="H50" s="92"/>
+      <c r="I50" s="92"/>
     </row>
     <row r="51" spans="7:9">
-      <c r="H51" s="97"/>
-      <c r="I51" s="97"/>
+      <c r="H51" s="92"/>
+      <c r="I51" s="92"/>
     </row>
     <row r="52" spans="7:9">
-      <c r="H52" s="97"/>
-      <c r="I52" s="97"/>
+      <c r="H52" s="92"/>
+      <c r="I52" s="92"/>
     </row>
     <row r="53" spans="7:9">
-      <c r="H53" s="97"/>
-      <c r="I53" s="97"/>
+      <c r="H53" s="92"/>
+      <c r="I53" s="92"/>
     </row>
     <row r="54" spans="7:9">
-      <c r="G54" s="99"/>
-      <c r="H54" s="97"/>
-      <c r="I54" s="97"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="92"/>
+      <c r="I54" s="92"/>
     </row>
     <row r="55" spans="7:9">
-      <c r="H55" s="97"/>
-      <c r="I55" s="97"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="92"/>
     </row>
     <row r="56" spans="7:9">
-      <c r="G56" s="99"/>
-      <c r="H56" s="97"/>
-      <c r="I56" s="97"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="92"/>
+      <c r="I56" s="92"/>
     </row>
     <row r="57" spans="7:9">
-      <c r="H57" s="97"/>
-      <c r="I57" s="97"/>
+      <c r="H57" s="92"/>
+      <c r="I57" s="92"/>
     </row>
     <row r="58" spans="7:9">
-      <c r="H58" s="97"/>
-      <c r="I58" s="97"/>
+      <c r="H58" s="92"/>
+      <c r="I58" s="92"/>
     </row>
     <row r="59" spans="7:9">
-      <c r="G59" s="99"/>
-      <c r="H59" s="97"/>
-      <c r="I59" s="97"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="92"/>
+      <c r="I59" s="92"/>
     </row>
     <row r="60" spans="7:9">
-      <c r="H60" s="97"/>
-      <c r="I60" s="97"/>
+      <c r="H60" s="92"/>
+      <c r="I60" s="92"/>
     </row>
     <row r="61" spans="7:9">
-      <c r="G61" s="99"/>
-      <c r="H61" s="97"/>
-      <c r="I61" s="97"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="92"/>
+      <c r="I61" s="92"/>
     </row>
     <row r="62" spans="7:9">
-      <c r="G62" s="99"/>
-      <c r="H62" s="97"/>
-      <c r="I62" s="97"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="92"/>
+      <c r="I62" s="92"/>
     </row>
     <row r="63" spans="7:9">
-      <c r="G63" s="100"/>
-      <c r="H63" s="97"/>
-      <c r="I63" s="97"/>
+      <c r="G63" s="94"/>
+      <c r="H63" s="92"/>
+      <c r="I63" s="92"/>
     </row>
     <row r="64" spans="7:9">
-      <c r="H64" s="97"/>
-      <c r="I64" s="97"/>
+      <c r="H64" s="92"/>
+      <c r="I64" s="92"/>
     </row>
     <row r="65" spans="7:9">
-      <c r="H65" s="97"/>
-      <c r="I65" s="97"/>
+      <c r="H65" s="92"/>
+      <c r="I65" s="92"/>
     </row>
     <row r="66" spans="7:9">
-      <c r="H66" s="97"/>
-      <c r="I66" s="97"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="92"/>
     </row>
     <row r="67" spans="7:9">
-      <c r="G67" s="99"/>
-      <c r="H67" s="97"/>
-      <c r="I67" s="97"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="92"/>
+      <c r="I67" s="92"/>
     </row>
     <row r="68" spans="7:9">
-      <c r="G68" s="99"/>
-      <c r="H68" s="97"/>
-      <c r="I68" s="97"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="92"/>
+      <c r="I68" s="92"/>
     </row>
     <row r="69" spans="7:9">
-      <c r="G69" s="99"/>
-      <c r="H69" s="97"/>
-      <c r="I69" s="97"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="92"/>
+      <c r="I69" s="92"/>
     </row>
     <row r="70" spans="7:9">
-      <c r="H70" s="97"/>
-      <c r="I70" s="97"/>
+      <c r="H70" s="92"/>
+      <c r="I70" s="92"/>
     </row>
     <row r="71" spans="7:9">
-      <c r="H71" s="97"/>
-      <c r="I71" s="97"/>
+      <c r="H71" s="92"/>
+      <c r="I71" s="92"/>
     </row>
     <row r="72" spans="7:9">
-      <c r="G72" s="99"/>
-      <c r="H72" s="97"/>
-      <c r="I72" s="97"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="92"/>
+      <c r="I72" s="92"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A33:C33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A7" r:id="rId1" display="TEL:918-831-6815"/>
@@ -2153,603 +2132,645 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:N53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.4196428571429" style="4" customWidth="1"/>
-    <col min="2" max="2" width="10.6696428571429" style="4" customWidth="1"/>
-    <col min="3" max="3" width="39" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.5803571428571" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.75" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.58035714285714" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11" style="6" customWidth="1"/>
-    <col min="8" max="8" width="7.08035714285714" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.3303571428571" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.58035714285714" style="4" customWidth="1"/>
-    <col min="11" max="11" width="9" style="7" customWidth="1"/>
-    <col min="12" max="12" width="10.0267857142857" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.4166666666667" style="6" customWidth="1"/>
+    <col min="2" max="2" width="10.6666666666667" style="6" customWidth="1"/>
+    <col min="3" max="3" width="39" style="6" customWidth="1"/>
+    <col min="4" max="4" width="13.5833333333333" style="5" customWidth="1"/>
+    <col min="5" max="5" width="9.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="8.58333333333333" style="7" customWidth="1"/>
+    <col min="7" max="7" width="11" style="8" customWidth="1"/>
+    <col min="8" max="8" width="7.08333333333333" style="6" customWidth="1"/>
+    <col min="9" max="9" width="11.3333333333333" style="5" customWidth="1"/>
+    <col min="10" max="10" width="9.58333333333333" style="6" customWidth="1"/>
+    <col min="11" max="11" width="9" style="9" customWidth="1"/>
+    <col min="12" max="12" width="10.025" style="6" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.8" customHeight="1" spans="1:13">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:13">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:13">
-      <c r="A3" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="12" customHeight="1" spans="1:13">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:13">
-      <c r="A5" s="14" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="15.5" spans="1:13">
+      <c r="A3" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="16" t="s">
+    </row>
+    <row r="4" s="2" customFormat="1" ht="12" customHeight="1" spans="1:13">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="15.5" spans="1:13">
+      <c r="A5" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="19" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="12"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:13">
-      <c r="A6" s="21"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="16" t="s">
+      <c r="D5" s="26"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="27"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="22"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:13">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="16" t="s">
+      <c r="K5" s="30"/>
+      <c r="L5" s="21"/>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="15.5" spans="1:13">
+      <c r="A6" s="31"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="17"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="6"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="5"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:13">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:13">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23" t="s">
+      <c r="D6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="32"/>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="15.5" spans="1:13">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="D7" s="26"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="27"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="20"/>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="15.5" spans="1:13">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" s="3" customFormat="1" ht="15.5" spans="1:13">
+      <c r="A9" s="33"/>
+      <c r="B9" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="C9" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="24"/>
-      <c r="I9" s="26" t="s">
+      <c r="F9" s="34"/>
+      <c r="G9" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="26" t="s">
+      <c r="H9" s="34"/>
+      <c r="I9" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="24"/>
-      <c r="M9" s="27" t="s">
+      <c r="J9" s="34"/>
+      <c r="K9" s="36" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:13">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="30"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:13">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="30"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="13.5" customHeight="1" spans="1:13">
-      <c r="E12" s="28"/>
-      <c r="G12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="M12" s="30"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="13.5" customHeight="1"/>
-    <row r="14" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:13">
-      <c r="A14" s="4"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-    </row>
-    <row r="15" s="3" customFormat="1" ht="18.35" customHeight="1" spans="1:13">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
-      <c r="L15" s="35"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:13">
-      <c r="A16" s="3" t="s">
+      <c r="L9" s="34"/>
+      <c r="M9" s="37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:13">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="39"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="39"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="40"/>
+    </row>
+    <row r="11" s="3" customFormat="1" ht="13.5" customHeight="1" spans="1:13">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="39"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="40"/>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="13.5" customHeight="1" spans="1:13">
+      <c r="E12" s="38"/>
+      <c r="G12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="M12" s="40"/>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="14" s="4" customFormat="1" ht="13.5" customHeight="1" spans="1:13">
+      <c r="A14" s="18"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+    </row>
+    <row r="15" s="4" customFormat="1" ht="18.35" customHeight="1" spans="1:13">
+      <c r="A15" s="44"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="45"/>
+    </row>
+    <row r="16" s="4" customFormat="1" ht="15.5" spans="1:13">
+      <c r="A16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="13">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="22">
         <f t="shared" ref="E16:I16" si="0">SUM(E10:E13)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="50">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="41" t="s">
+      <c r="H16" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="51">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="41" t="s">
+      <c r="J16" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="51">
         <f>SUM(K10:K13)</f>
         <v>0</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="M16" s="41">
+      <c r="M16" s="51">
         <f>SUM(M10:M13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:14">
-      <c r="A17" s="42"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:14">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="4"/>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:14">
-      <c r="A19" s="43" t="s">
+    <row r="17" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="A17" s="52"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+    </row>
+    <row r="18" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="18"/>
+      <c r="N18" s="2"/>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="A19" s="53" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="43"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="4"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:14">
-      <c r="A20" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="7">
+      <c r="B19" s="18"/>
+      <c r="C19" s="53"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="18"/>
+    </row>
+    <row r="20" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="A20" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="11">
         <f>M16</f>
         <v>0</v>
       </c>
-      <c r="C20" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="4"/>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="1:14">
-      <c r="A21" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="43"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="4"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:14">
-      <c r="A24" s="44"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="46"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:14">
-      <c r="F25" s="4"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="49"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:14">
-      <c r="F26" s="4"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="49"/>
-    </row>
-    <row r="27" s="3" customFormat="1" spans="1:14">
-      <c r="F27" s="4"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="49"/>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:14">
-      <c r="F28" s="4"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="49"/>
-    </row>
-    <row r="29" s="3" customFormat="1" spans="1:14">
-      <c r="F29" s="4"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="49"/>
-    </row>
-    <row r="30" s="3" customFormat="1" spans="1:14">
-      <c r="F30" s="4"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="49"/>
-    </row>
-    <row r="31" s="3" customFormat="1" spans="1:14">
-      <c r="F31" s="4"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="49"/>
-    </row>
-    <row r="32" s="3" customFormat="1" spans="1:14">
-      <c r="F32" s="4"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="40"/>
-      <c r="L32" s="49"/>
-    </row>
-    <row r="33" s="3" customFormat="1" spans="6:12">
-      <c r="F33" s="4"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="40"/>
-      <c r="L33" s="49"/>
-    </row>
-    <row r="34" s="3" customFormat="1" spans="6:12">
-      <c r="F34" s="4"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="49"/>
-    </row>
-    <row r="35" s="3" customFormat="1" spans="6:12">
-      <c r="F35" s="4"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="40"/>
-      <c r="L35" s="49"/>
-    </row>
-    <row r="36" s="3" customFormat="1" spans="6:12">
-      <c r="F36" s="4"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="40"/>
-      <c r="L36" s="49"/>
-    </row>
-    <row r="37" s="3" customFormat="1" spans="6:12">
-      <c r="F37" s="4"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="40"/>
-      <c r="L37" s="49"/>
-    </row>
-    <row r="38" s="3" customFormat="1" spans="6:12">
-      <c r="F38" s="4"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="40"/>
-      <c r="L38" s="49"/>
-    </row>
-    <row r="39" s="3" customFormat="1" spans="6:12">
-      <c r="F39" s="4"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="40"/>
-      <c r="L39" s="49"/>
-    </row>
-    <row r="40" s="3" customFormat="1" spans="6:12">
-      <c r="F40" s="4"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="40"/>
-      <c r="L40" s="49"/>
-    </row>
-    <row r="41" s="3" customFormat="1" spans="6:12">
-      <c r="F41" s="4"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="49"/>
-    </row>
-    <row r="42" s="3" customFormat="1" spans="6:12">
-      <c r="F42" s="4"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="40"/>
-      <c r="L42" s="49"/>
-    </row>
-    <row r="43" s="3" customFormat="1" spans="6:12">
-      <c r="F43" s="4"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="40"/>
-      <c r="L43" s="49"/>
-    </row>
-    <row r="44" s="3" customFormat="1" spans="6:12">
-      <c r="F44" s="4"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="40"/>
-      <c r="L44" s="49"/>
-    </row>
-    <row r="45" s="3" customFormat="1" spans="6:12">
-      <c r="F45" s="4"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="40"/>
-      <c r="L45" s="49"/>
-    </row>
-    <row r="46" s="3" customFormat="1" spans="6:12">
-      <c r="F46" s="4"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="40"/>
-      <c r="L46" s="49"/>
-    </row>
-    <row r="47" s="3" customFormat="1" spans="6:12">
-      <c r="F47" s="4"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="40"/>
-      <c r="L47" s="49"/>
-    </row>
-    <row r="48" s="3" customFormat="1" spans="6:12">
-      <c r="F48" s="4"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="40"/>
-      <c r="L48" s="49"/>
-    </row>
-    <row r="49" s="3" customFormat="1" spans="6:12">
-      <c r="F49" s="4"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="40"/>
-      <c r="L49" s="49"/>
-    </row>
-    <row r="50" s="3" customFormat="1" spans="6:12">
-      <c r="F50" s="4"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="40"/>
-      <c r="L50" s="49"/>
-    </row>
-    <row r="51" s="3" customFormat="1" spans="6:12">
-      <c r="F51" s="4"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="40"/>
-      <c r="L51" s="49"/>
-    </row>
-    <row r="52" s="3" customFormat="1" spans="6:12">
-      <c r="F52" s="4"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="40"/>
-      <c r="L52" s="49"/>
-    </row>
-    <row r="53" s="3" customFormat="1" spans="6:12">
-      <c r="F53" s="4"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="40"/>
-      <c r="L53" s="49"/>
+      <c r="C20" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="20"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="18"/>
+    </row>
+    <row r="21" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="A21" s="53" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="53"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="18"/>
+    </row>
+    <row r="22" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="18"/>
+    </row>
+    <row r="23" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="18"/>
+    </row>
+    <row r="24" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="A24" s="54"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="56"/>
+    </row>
+    <row r="25" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="F25" s="18"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="F26" s="18"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="27"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="12"/>
+    </row>
+    <row r="27" s="4" customFormat="1" ht="15.5" spans="1:14">
+      <c r="F27" s="18"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="12"/>
+    </row>
+    <row r="28" s="5" customFormat="1" spans="1:14">
+      <c r="F28" s="6"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="60"/>
+    </row>
+    <row r="29" s="5" customFormat="1" spans="1:14">
+      <c r="F29" s="6"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="60"/>
+    </row>
+    <row r="30" s="5" customFormat="1" spans="1:14">
+      <c r="F30" s="6"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="60"/>
+    </row>
+    <row r="31" s="5" customFormat="1" spans="1:14">
+      <c r="F31" s="6"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="59"/>
+      <c r="L31" s="60"/>
+    </row>
+    <row r="32" s="5" customFormat="1" spans="1:14">
+      <c r="F32" s="6"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="60"/>
+    </row>
+    <row r="33" s="5" customFormat="1" spans="6:12">
+      <c r="F33" s="6"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="59"/>
+      <c r="L33" s="60"/>
+    </row>
+    <row r="34" s="5" customFormat="1" spans="6:12">
+      <c r="F34" s="6"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="59"/>
+      <c r="L34" s="60"/>
+    </row>
+    <row r="35" s="5" customFormat="1" spans="6:12">
+      <c r="F35" s="6"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="59"/>
+      <c r="L35" s="60"/>
+    </row>
+    <row r="36" s="5" customFormat="1" spans="6:12">
+      <c r="F36" s="6"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="59"/>
+      <c r="L36" s="60"/>
+    </row>
+    <row r="37" s="5" customFormat="1" spans="6:12">
+      <c r="F37" s="6"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="60"/>
+    </row>
+    <row r="38" s="5" customFormat="1" spans="6:12">
+      <c r="F38" s="6"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="59"/>
+      <c r="L38" s="60"/>
+    </row>
+    <row r="39" s="5" customFormat="1" spans="6:12">
+      <c r="F39" s="6"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="59"/>
+      <c r="L39" s="60"/>
+    </row>
+    <row r="40" s="5" customFormat="1" spans="6:12">
+      <c r="F40" s="6"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="59"/>
+      <c r="L40" s="60"/>
+    </row>
+    <row r="41" s="5" customFormat="1" spans="6:12">
+      <c r="F41" s="6"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="59"/>
+      <c r="L41" s="60"/>
+    </row>
+    <row r="42" s="5" customFormat="1" spans="6:12">
+      <c r="F42" s="6"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="59"/>
+      <c r="L42" s="60"/>
+    </row>
+    <row r="43" s="5" customFormat="1" spans="6:12">
+      <c r="F43" s="6"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="59"/>
+      <c r="L43" s="60"/>
+    </row>
+    <row r="44" s="5" customFormat="1" spans="6:12">
+      <c r="F44" s="6"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="59"/>
+      <c r="L44" s="60"/>
+    </row>
+    <row r="45" s="5" customFormat="1" spans="6:12">
+      <c r="F45" s="6"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="59"/>
+      <c r="L45" s="60"/>
+    </row>
+    <row r="46" s="5" customFormat="1" spans="6:12">
+      <c r="F46" s="6"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="59"/>
+      <c r="L46" s="60"/>
+    </row>
+    <row r="47" s="5" customFormat="1" spans="6:12">
+      <c r="F47" s="6"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="59"/>
+      <c r="L47" s="60"/>
+    </row>
+    <row r="48" s="5" customFormat="1" spans="6:12">
+      <c r="F48" s="6"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="59"/>
+      <c r="L48" s="60"/>
+    </row>
+    <row r="49" s="5" customFormat="1" spans="6:12">
+      <c r="F49" s="6"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="59"/>
+      <c r="L49" s="60"/>
+    </row>
+    <row r="50" s="5" customFormat="1" spans="6:12">
+      <c r="F50" s="6"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="59"/>
+      <c r="L50" s="60"/>
+    </row>
+    <row r="51" s="5" customFormat="1" spans="6:12">
+      <c r="F51" s="6"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="59"/>
+      <c r="L51" s="60"/>
+    </row>
+    <row r="52" s="5" customFormat="1" spans="6:12">
+      <c r="F52" s="6"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="60"/>
+    </row>
+    <row r="53" s="5" customFormat="1" spans="6:12">
+      <c r="F53" s="6"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="59"/>
+      <c r="L53" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:L3"/>
@@ -2758,7 +2779,6 @@
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A22:D22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
